--- a/form/PAC_Improve_论文图表整理_v1.xlsx
+++ b/form/PAC_Improve_论文图表整理_v1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="30720" windowHeight="12744" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="论文图表总览" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="142">
   <si>
     <t>PAC-Test Improve 实验结果图表整理（v2 当前数据）</t>
-  </si>
-  <si>
-    <t>口径：原 ABC full 480 条 + PAC-C/27B 补跑 60 条；当前主指标按 540 条成功配对响应统计，数值保留一位小数。</t>
   </si>
   <si>
     <t>总体提升
@@ -124,9 +121,6 @@
     <t>主结果表：能力轴 x 模型</t>
   </si>
   <si>
-    <t>展示论文正文可引用的主结果；不包含 prompt 文本、队列信息或原始样本内容。</t>
-  </si>
-  <si>
     <t>表 1. 各能力轴与模型组合的 Prompt 增强效果</t>
   </si>
   <si>
@@ -223,21 +217,12 @@
     <t>高基线下仍有稳定增益，错误主要被压缩到少数样本。</t>
   </si>
   <si>
-    <t>表中“修复/回退”表示相对 baseline 的样本级方向变化，仅用于辅助判断稳定性；正文优先报告准确率、提升幅度与必要边界条件。</t>
-  </si>
-  <si>
     <t>表 2. 模型-能力轴提升矩阵 (pp)</t>
   </si>
   <si>
-    <t>矩阵读法：绿色越深表示提升越大；当前九个模型-能力轴主格均已形成 60 条完整配对样本。PAC-A / 9B 是唯一负向主格，应作为边界条件报告。</t>
-  </si>
-  <si>
     <t>分层结果：位置、干扰强度与绑定负载</t>
   </si>
   <si>
-    <t>分层图表用于解释提升来自哪些条件，不展示底层样本文本或 prompt 细节。</t>
-  </si>
-  <si>
     <t>图 3A. PAC-A：目标位置分层</t>
   </si>
   <si>
@@ -289,9 +274,6 @@
     <t>图表说明</t>
   </si>
   <si>
-    <t>面向论文写作的图表解释：仅保留读者需要理解的指标、现象与边界条件。</t>
-  </si>
-  <si>
     <t>图表</t>
   </si>
   <si>
@@ -419,9 +401,6 @@
   </si>
   <si>
     <t>附注与统计口径</t>
-  </si>
-  <si>
-    <t>用于论文图表脚注或方法段落的简写版本。</t>
   </si>
   <si>
     <t>项目</t>
@@ -1084,7 +1063,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3722,9 +3701,7 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3753,19 +3730,19 @@
     </row>
     <row r="4" ht="15" spans="1:12">
       <c r="A4" s="17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -3817,7 +3794,7 @@
     </row>
     <row r="8" ht="16.2" spans="1:12">
       <c r="A8" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -3833,22 +3810,22 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:12">
       <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -3859,7 +3836,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:12">
       <c r="A10" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="10">
         <v>0.45</v>
@@ -3874,7 +3851,7 @@
         <v>180</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -3885,7 +3862,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:12">
       <c r="A11" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="12">
         <v>0.466666666666667</v>
@@ -3900,7 +3877,7 @@
         <v>180</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -3911,7 +3888,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:12">
       <c r="A12" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="10">
         <v>0.716666666666667</v>
@@ -3926,7 +3903,7 @@
         <v>180</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -3965,7 +3942,7 @@
     </row>
     <row r="15" ht="15" spans="1:12">
       <c r="A15" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -4023,7 +4000,7 @@
     </row>
     <row r="19" ht="16.2" spans="1:12">
       <c r="A19" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4039,22 +4016,22 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:12">
       <c r="A20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F20" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -4065,7 +4042,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:12">
       <c r="A21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="5">
         <v>180</v>
@@ -4080,7 +4057,7 @@
         <v>21.7</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -4091,7 +4068,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:12">
       <c r="A22" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="7">
         <v>180</v>
@@ -4106,7 +4083,7 @@
         <v>16.1</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -4117,7 +4094,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:12">
       <c r="A23" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="5">
         <v>180</v>
@@ -4132,7 +4109,7 @@
         <v>18.9</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -4499,7 +4476,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4512,9 +4489,7 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:10">
-      <c r="A2" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4539,7 +4514,7 @@
     </row>
     <row r="4" ht="16.2" spans="1:10">
       <c r="A4" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4553,45 +4528,45 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:10">
       <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:10">
       <c r="A6" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="5">
         <v>60</v>
@@ -4606,24 +4581,24 @@
         <v>-1.7</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:10">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="7">
         <v>60</v>
@@ -4638,24 +4613,24 @@
         <v>35</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:10">
       <c r="A8" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="5">
         <v>60</v>
@@ -4670,24 +4645,24 @@
         <v>18.3</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:10">
       <c r="A9" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="7">
         <v>60</v>
@@ -4702,24 +4677,24 @@
         <v>33.3</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:10">
       <c r="A10" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="5">
         <v>60</v>
@@ -4734,24 +4709,24 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:10">
       <c r="A11" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="7">
         <v>60</v>
@@ -4766,24 +4741,24 @@
         <v>28.3</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:10">
       <c r="A12" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="5">
         <v>60</v>
@@ -4798,24 +4773,24 @@
         <v>33.3</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:10">
       <c r="A13" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="7">
         <v>60</v>
@@ -4830,24 +4805,24 @@
         <v>10</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:10">
       <c r="A14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="5">
         <v>60</v>
@@ -4862,13 +4837,13 @@
         <v>10</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:10">
@@ -4884,9 +4859,7 @@
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="A16" s="16"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -4935,7 +4908,7 @@
     </row>
     <row r="20" ht="16.2" spans="1:10">
       <c r="A20" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -4949,21 +4922,19 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="16" t="s">
-        <v>64</v>
-      </c>
+      <c r="F21" s="16"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -4971,7 +4942,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:10">
       <c r="A22" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="14">
         <v>-1.7</v>
@@ -4991,7 +4962,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:10">
       <c r="A23" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="15">
         <v>33.3</v>
@@ -5011,7 +4982,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:10">
       <c r="A24" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="15">
         <v>33.3</v>
@@ -5299,7 +5270,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5314,9 +5285,7 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -5345,7 +5314,7 @@
     </row>
     <row r="4" ht="16.2" spans="1:12">
       <c r="A4" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5361,19 +5330,19 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:12">
       <c r="A5" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -5589,7 +5558,7 @@
     </row>
     <row r="17" ht="16.2" spans="1:12">
       <c r="A17" s="9" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -5605,22 +5574,22 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -5899,7 +5868,7 @@
     </row>
     <row r="33" ht="16.2" spans="1:12">
       <c r="A33" s="9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -5915,19 +5884,19 @@
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:12">
       <c r="A34" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -5939,7 +5908,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:12">
       <c r="A35" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B35" s="10">
         <v>0.476190476190476</v>
@@ -5963,7 +5932,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:12">
       <c r="A36" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B36" s="12">
         <v>0.695652173913043</v>
@@ -5987,7 +5956,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:12">
       <c r="A37" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B37" s="10">
         <v>0.476190476190476</v>
@@ -6011,7 +5980,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:12">
       <c r="A38" s="7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B38" s="12">
         <v>0.736842105263158</v>
@@ -6035,7 +6004,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:12">
       <c r="A39" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B39" s="10">
         <v>0.789473684210526</v>
@@ -6059,7 +6028,7 @@
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:12">
       <c r="A40" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B40" s="12">
         <v>0.789473684210526</v>
@@ -6083,7 +6052,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:12">
       <c r="A41" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B41" s="10">
         <v>0.833333333333333</v>
@@ -6107,7 +6076,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:12">
       <c r="A42" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B42" s="12">
         <v>0.818181818181818</v>
@@ -6131,7 +6100,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:12">
       <c r="A43" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B43" s="10">
         <v>0.888888888888889</v>
@@ -6615,7 +6584,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6624,9 +6593,7 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -6643,142 +6610,142 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" ht="46.5" customHeight="1" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="46.5" customHeight="1" spans="1:6">
       <c r="A6" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" ht="46.5" customHeight="1" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="46.5" customHeight="1" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="46.5" customHeight="1" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" ht="46.5" customHeight="1" spans="1:6">
       <c r="A10" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:6">
@@ -6995,14 +6962,12 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:2">
-      <c r="A2" s="3" t="s">
-        <v>128</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
     <row r="3" ht="15" spans="1:2">
@@ -7011,82 +6976,82 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:2">
       <c r="A8" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:2">
       <c r="A10" s="7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:2">
       <c r="A12" s="7" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:2">
